--- a/outputs/daily/hr_rankings_2026-08-18.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-18.xlsx
@@ -7672,7 +7672,7 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>53.2</v>
+        <v>53.4</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>60</v>
       </c>
       <c r="U27" t="n">
-        <v>65.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -7761,22 +7761,22 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
@@ -17920,7 +17920,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>78</v>
       </c>
       <c r="U65" t="n">
-        <v>9.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -18024,7 +18024,7 @@
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Last 7 games: 4/23, 0 HR</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-18.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-18.xlsx
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -22600,7 +22600,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -23440,7 +23440,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -24000,7 +24000,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -24280,7 +24280,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -24560,7 +24560,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -25120,7 +25120,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -26240,7 +26240,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -27080,7 +27080,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -27360,7 +27360,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -28200,7 +28200,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -29600,7 +29600,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -30160,7 +30160,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -30720,7 +30720,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -32120,7 +32120,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -34080,7 +34080,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -34920,7 +34920,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -35200,7 +35200,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -37206,7 +37206,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -37766,7 +37766,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -38606,7 +38606,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -39726,7 +39726,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -40006,7 +40006,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -40286,7 +40286,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -41686,7 +41686,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-18.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-18.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>69.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>52.9</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>58.9</v>
+        <v>59</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>47.5</v>
       </c>
       <c r="R8" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5568,7 +5568,7 @@
         <v>47.5</v>
       </c>
       <c r="R19" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S19" t="n">
         <v>94.90000000000001</v>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -5824,7 +5824,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>52.9</v>
       </c>
       <c r="R20" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S20" t="n">
         <v>86.40000000000001</v>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>52.9</v>
       </c>
       <c r="R25" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S25" t="n">
         <v>64.3</v>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8064,7 +8064,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>52.9</v>
       </c>
       <c r="R28" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S28" t="n">
         <v>76.2</v>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>47.5</v>
       </c>
       <c r="R32" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S32" t="n">
         <v>86.40000000000001</v>
@@ -9399,7 +9399,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>52.9</v>
       </c>
       <c r="R34" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S34" t="n">
         <v>93.2</v>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>47.5</v>
       </c>
       <c r="R35" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S35" t="n">
         <v>64.3</v>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -10864,7 +10864,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>52.9</v>
       </c>
       <c r="R38" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S38" t="n">
         <v>52.4</v>
@@ -11079,7 +11079,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI38" t="inlineStr">
@@ -11375,47 +11375,47 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>670623</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-19T00:40:00Z</t>
+          <t>2026-08-19T00:10:00Z</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Ryan Feltner</t>
+          <t>George Klassen</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>663372</t>
+          <t>691946</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -11438,26 +11438,26 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>23.2</v>
+        <v>18.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>44.6</v>
+        <v>52.9</v>
       </c>
       <c r="R40" t="n">
-        <v>58.2</v>
+        <v>41.6</v>
       </c>
       <c r="S40" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T40" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U40" t="n">
-        <v>27.6</v>
+        <v>55.9</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -11492,7 +11492,7 @@
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr"/>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Contact streak: 10/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.9% barrel, 13.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 13.0% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
@@ -11539,112 +11539,112 @@
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>99.3976</t>
+          <t>96.9533</t>
         </is>
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>0.3823</t>
+          <t>0.3779</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>0.1202</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr">
         <is>
-          <t>0.3154</t>
+          <t>0.3214</t>
         </is>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>70.45</t>
+          <t>67.81</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>30.94</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>0.1402</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>38.08</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>88.25</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="BD40" t="inlineStr">
         <is>
-          <t>0.4449</t>
+          <t>0.433</t>
         </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="BG40" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI40" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ40" t="inlineStr"/>
@@ -11655,27 +11655,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>670623</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-19T00:10:00Z</t>
+          <t>2026-08-19T00:40:00Z</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -11685,17 +11685,17 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>George Klassen</t>
+          <t>Ryan Feltner</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>691946</t>
+          <t>663372</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -11718,26 +11718,26 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>18.6</v>
+        <v>23.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>52.9</v>
+        <v>44.6</v>
       </c>
       <c r="R41" t="n">
-        <v>41.1</v>
+        <v>58.2</v>
       </c>
       <c r="S41" t="n">
-        <v>96.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T41" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U41" t="n">
-        <v>55.9</v>
+        <v>27.6</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -11772,7 +11772,7 @@
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr"/>
@@ -11789,12 +11789,12 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Contact streak: 10/27 over last 7 games</t>
+          <t>Last 7 games: 4/22, 1 HR</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 13.0% barrel, 2.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.9% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -11819,112 +11819,112 @@
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>96.9533</t>
+          <t>99.3976</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>0.3779</t>
+          <t>0.3823</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.1202</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>0.3214</t>
+          <t>0.3154</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>67.81</t>
+          <t>70.45</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.1402</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>38.08</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>88.25</t>
         </is>
       </c>
       <c r="BD41" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>0.4449</t>
         </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="BF41" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="BG41" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI41" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ41" t="inlineStr"/>
@@ -11960,7 +11960,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -13128,7 +13128,7 @@
         <v>47.5</v>
       </c>
       <c r="R46" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S46" t="n">
         <v>96.59999999999999</v>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI46" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -15344,7 +15344,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>52.9</v>
       </c>
       <c r="R54" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S54" t="n">
         <v>94.90000000000001</v>
@@ -15559,7 +15559,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI54" t="inlineStr">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -15624,7 +15624,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>47.5</v>
       </c>
       <c r="R55" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S55" t="n">
         <v>93.2</v>
@@ -15839,7 +15839,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI55" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -15928,7 +15928,7 @@
         <v>47.5</v>
       </c>
       <c r="R56" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S56" t="n">
         <v>76.2</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI56" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -17608,7 +17608,7 @@
         <v>52.9</v>
       </c>
       <c r="R62" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S62" t="n">
         <v>44.8</v>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI62" t="inlineStr">
@@ -17840,7 +17840,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -18095,27 +18095,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>678391</t>
+          <t>694203</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jorbit Vivas</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-19T00:05:00Z</t>
+          <t>2026-08-19T00:10:00Z</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -18125,17 +18125,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Cal Quantrill</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>615698</t>
+          <t>664299</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -18144,7 +18144,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -18158,26 +18158,26 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>4.5</v>
+        <v>24.9</v>
       </c>
       <c r="Q64" t="n">
-        <v>47.3</v>
+        <v>47.5</v>
       </c>
       <c r="R64" t="n">
-        <v>42.1</v>
+        <v>41.6</v>
       </c>
       <c r="S64" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T64" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U64" t="n">
-        <v>34.9</v>
+        <v>23.7</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -18229,12 +18229,12 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -18244,112 +18244,112 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Contact streak: 6/17 over last 7 games</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 12.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 5.1 HR allowed</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>36.46</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>83.52</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>95.1412</t>
+          <t>98.1241</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>0.3212</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>0.0778</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>0.2996</t>
+          <t>0.2553</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>73.43</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>34.22</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>25.38</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.0862</t>
+          <t>0.1313</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>88.93</t>
+          <t>90.02</t>
         </is>
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>0.4484</t>
+          <t>0.4362</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>0.1877</t>
+          <t>0.1768</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>39.92</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr">
@@ -18359,12 +18359,12 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr"/>
@@ -18375,47 +18375,47 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>694203</t>
+          <t>678391</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Jorbit Vivas</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-19T00:10:00Z</t>
+          <t>2026-08-19T00:05:00Z</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>Cal Quantrill</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>664299</t>
+          <t>615698</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -18438,26 +18438,26 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>24.9</v>
+        <v>4.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>47.5</v>
+        <v>47.3</v>
       </c>
       <c r="R65" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S65" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T65" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U65" t="n">
-        <v>23.7</v>
+        <v>34.9</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -18509,12 +18509,12 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -18524,112 +18524,112 @@
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Contact streak: 6/17 over last 7 games</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 5.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 12.9 HR allowed</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>36.46</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>83.52</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>98.1241</t>
+          <t>95.1412</t>
         </is>
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.3212</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.0778</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr">
         <is>
-          <t>0.2553</t>
+          <t>0.2996</t>
         </is>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>73.43</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>34.22</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>25.38</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>0.1313</t>
+          <t>0.0862</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>90.02</t>
+          <t>88.93</t>
         </is>
       </c>
       <c r="BD65" t="inlineStr">
         <is>
-          <t>0.4362</t>
+          <t>0.4484</t>
         </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
-          <t>0.1768</t>
+          <t>0.1877</t>
         </is>
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>39.92</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="BG65" t="inlineStr">
@@ -18639,12 +18639,12 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI65" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ65" t="inlineStr"/>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -20128,7 +20128,7 @@
         <v>47</v>
       </c>
       <c r="R71" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S71" t="n">
         <v>44.8</v>
@@ -20319,7 +20319,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI71" t="inlineStr">
@@ -21526,7 +21526,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -22110,7 +22110,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>69.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>52.9</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -22325,7 +22325,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -22646,7 +22646,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -22926,7 +22926,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22950,7 +22950,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>58.9</v>
+        <v>59</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>47.5</v>
       </c>
       <c r="R8" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -23165,7 +23165,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -23206,7 +23206,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -23486,7 +23486,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -24046,7 +24046,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -26006,7 +26006,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -26054,7 +26054,7 @@
         <v>47.5</v>
       </c>
       <c r="R19" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S19" t="n">
         <v>94.90000000000001</v>
@@ -26245,7 +26245,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -26286,7 +26286,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -26310,7 +26310,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>52.9</v>
       </c>
       <c r="R20" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S20" t="n">
         <v>86.40000000000001</v>
@@ -26525,7 +26525,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
